--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_r2/post_rank_positive_return/staggered_5d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_r2/post_rank_positive_return/staggered_5d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -488,30 +494,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>基准收益</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>超额收益</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>年化波动</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪误差</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>信息比率</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>策略最大回撤</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>基准最大回撤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>超额最大回撤</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Calmar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>年化换手率（单边）</t>
         </is>
@@ -527,21 +563,39 @@
         <v>0.05470166970721468</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>-0.02176047699359285</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.07816301110572166</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0.2922826881128781</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="F2" s="3" t="n">
+        <v>0.2438377301636006</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0.3005612218251933</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.430449912317964</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="I2" s="4" t="n">
+        <v>0.4571107711179032</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0.1999498520809592</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="K2" s="3" t="n">
+        <v>0.1506490308477421</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.2000161036570859</v>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>0.3102368163097152</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>22.73201231281142</v>
       </c>
     </row>
@@ -555,21 +609,39 @@
         <v>-0.2475236132145736</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>-0.2255774308756096</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-0.02833876905702504</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.2338293769283012</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0.1645625372113714</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>-1.212527619339336</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>-1.577770433139014</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="I3" s="4" t="n">
+        <v>-0.1473654803744533</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.2837749520842454</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="K3" s="3" t="n">
+        <v>0.2845881262232945</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1613542712052681</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>-0.9032318155039534</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>22.43199595098364</v>
       </c>
     </row>
@@ -583,21 +655,39 @@
         <v>-0.1245125673908584</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>-0.1141699148043651</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-0.01167566191230762</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0.2187744462884846</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0.1713354781526617</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>-0.5917696623101286</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>-0.8267297342418364</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="I4" s="4" t="n">
+        <v>0.01467490063295581</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.26391959998013</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="K4" s="3" t="n">
+        <v>0.2177913835362562</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1478049765677822</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>-0.4899598771017034</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>23.59977386177457</v>
       </c>
     </row>
@@ -611,21 +701,39 @@
         <v>0.002432737098540416</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.1298071537204202</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.1127399629241522</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0.274333295794483</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0.1475963477575598</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.08886996784611688</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.153660123784514</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="I5" s="4" t="n">
+        <v>-0.7688191857441971</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.2844274502528309</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="K5" s="3" t="n">
+        <v>0.1515696200238076</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.2125711885957432</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>0.008906983674179343</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>26.16844736068498</v>
       </c>
     </row>
@@ -639,54 +747,90 @@
         <v>0.243141712302994</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0.2243203183030871</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.01537293281711882</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0.2651422222990683</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0.1575587204815958</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>0.9283010762737436</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1.307239475075883</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="I6" s="4" t="n">
+        <v>0.2349060183354419</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>0.1918275468986169</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0.1188658802983931</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.148044997199189</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>1.319950858429839</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>25.61768176320768</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026年截至07-31</t>
+          <t>2026年截至07-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1365662766284543</v>
+        <v>0.1364338398947549</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3435313318893911</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.8039660606264581</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1.11893876574527</v>
+        <v>-0.01504143451691176</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.1537884736677961</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.344779918425992</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0.2164059973328002</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.8065550237167097</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.122562054684861</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1.360441695560327</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>0.1752348567316947</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.490679550768987</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>23.38252562476805</v>
+      <c r="K7" s="3" t="n">
+        <v>0.127969093077366</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.09322459423257268</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.501259698188257</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>23.30435549403406</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>